--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -611,7 +611,7 @@
     <t>healthCarePartyType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHealthCarePartyType}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHealthCarePartyType}
 </t>
   </si>
   <si>
@@ -635,7 +635,7 @@
     <t>communicationType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleCommunicationType}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleCommunicationType}
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <t>healthCarePartyDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHealthCarePartyDepartment}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHealthcarePartyDepartment}
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHealthCarePartyDepartment</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHealthcarePartyDepartment</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -832,7 +832,7 @@
     <t>ward</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleWard}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleWard}
 </t>
   </si>
   <si>
@@ -845,7 +845,7 @@
     <t>PractitionerRole.extension:ward.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleWard</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleWard</t>
   </si>
   <si>
     <t>PractitionerRole.extension:ward.value[x]</t>
@@ -881,7 +881,7 @@
     <t>section</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleSection}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleSection}
 </t>
   </si>
   <si>
@@ -894,7 +894,7 @@
     <t>PractitionerRole.extension:section.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleSection</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleSection</t>
   </si>
   <si>
     <t>PractitionerRole.extension:section.value[x]</t>
@@ -930,7 +930,7 @@
     <t>hospital</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHospital}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHospital}
 </t>
   </si>
   <si>
@@ -943,7 +943,7 @@
     <t>PractitionerRole.extension:hospital.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHospital</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHospital</t>
   </si>
   <si>
     <t>PractitionerRole.extension:hospital.value[x]</t>
@@ -979,7 +979,7 @@
     <t>hcpRoleName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHcpRoleName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHcpRoleName}
 </t>
   </si>
   <si>
@@ -992,7 +992,7 @@
     <t>PractitionerRole.extension:hcpRoleName.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHcpRoleName</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHcpRoleName</t>
   </si>
   <si>
     <t>PractitionerRole.extension:hcpRoleName.value[x]</t>
@@ -1013,7 +1013,7 @@
     <t>userRoleDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleDepartment}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleDepartment}
 </t>
   </si>
   <si>
@@ -1026,7 +1026,7 @@
     <t>PractitionerRole.extension:userRoleDepartment.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleDepartment</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleDepartment</t>
   </si>
   <si>
     <t>PractitionerRole.extension:userRoleDepartment.value[x]</t>
@@ -1062,7 +1062,7 @@
     <t>dipsSignature</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleDipsSignature}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleDipsSignature}
 </t>
   </si>
   <si>
@@ -1075,7 +1075,7 @@
     <t>PractitionerRole.extension:dipsSignature.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleDipsSignature</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleDipsSignature</t>
   </si>
   <si>
     <t>PractitionerRole.extension:dipsSignature.value[x]</t>
@@ -1093,7 +1093,7 @@
     <t>userRoleLastUpdated</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleLastUpdated}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleLastUpdated}
 </t>
   </si>
   <si>
@@ -1106,7 +1106,7 @@
     <t>PractitionerRole.extension:userRoleLastUpdated.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleLastUpdated</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleLastUpdated</t>
   </si>
   <si>
     <t>PractitionerRole.extension:userRoleLastUpdated.value[x]</t>
@@ -1131,7 +1131,7 @@
     <t>healthCarePosition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHealthCarePosition}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHealthCarePosition}
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>PractitionerRole.extension:healthCarePosition.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleHealthCarePosition</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleHealthCarePosition</t>
   </si>
   <si>
     <t>PractitionerRole.extension:healthCarePosition.value[x]</t>
@@ -1304,7 +1304,7 @@
     <t>userRoleName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleName}
 </t>
   </si>
   <si>
@@ -1317,7 +1317,7 @@
     <t>PractitionerRole.extension:userRoleName.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleName</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleName</t>
   </si>
   <si>
     <t>PractitionerRole.extension:userRoleName.value[x]</t>
@@ -1335,7 +1335,7 @@
     <t>userRoleId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleId}
 </t>
   </si>
   <si>
@@ -1348,7 +1348,7 @@
     <t>PractitionerRole.extension:userRoleId.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleUserRoleId</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleUserRoleId</t>
   </si>
   <si>
     <t>PractitionerRole.extension:userRoleId.value[x]</t>

--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRole.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRole.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
